--- a/product_upload/packages/16/file.xlsx
+++ b/product_upload/packages/16/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -844,6 +849,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>DERMOVATE CREAM 0.05%</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-613CC1F4FC3E</t>
         </is>
       </c>
@@ -867,7 +877,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1038,6 +1048,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>DERMOVATE OINTMENT 0.05%</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-ADC64AD9658B</t>
         </is>
       </c>
@@ -1061,7 +1076,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1224,6 +1239,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>DEXANOL CREAM 30 GM</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-4CBF2DEC59C2</t>
         </is>
       </c>
@@ -1247,7 +1267,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1410,6 +1430,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>DEXAFLOX OPHTHALMIC SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-F48462C19308</t>
         </is>
       </c>
@@ -1433,7 +1458,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1604,6 +1629,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>DETRUSITOL RETARD 4 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-FEFDCFD5E0FA</t>
         </is>
       </c>
@@ -1627,7 +1657,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1790,6 +1820,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>DETRUSITOL RETARD 2 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-A7DBA6BC7442</t>
         </is>
       </c>
@@ -1813,7 +1848,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1988,6 +2023,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>DETRUSITOL 2 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-B40DB13DA04B</t>
         </is>
       </c>
@@ -2011,7 +2051,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2182,6 +2222,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>DESLOR 5 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-E826C7F2772F</t>
         </is>
       </c>
@@ -2205,7 +2250,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2372,6 +2417,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>DEWAX 5MG-ML OTIC DROPS</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-B5481ED60F2B</t>
         </is>
       </c>
@@ -2395,7 +2445,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2562,6 +2612,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>DEPRAN 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-BD30DB81E296</t>
         </is>
       </c>
@@ -2585,7 +2640,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2752,6 +2807,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>DEPRAN 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-E87E93021E27</t>
         </is>
       </c>
@@ -2775,7 +2835,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2942,6 +3002,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>DEPRALEX 20MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-3C703D036E16</t>
         </is>
       </c>
@@ -2965,7 +3030,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3124,6 +3189,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>DEFLAT 40 MG/ML ORAL DROPS</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-645A7E629913</t>
         </is>
       </c>
@@ -3147,7 +3217,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3310,6 +3380,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>DEFLAT</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-BC6B6B0E7477</t>
         </is>
       </c>
@@ -3333,7 +3408,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3500,6 +3575,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>DEFLAT</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-1C09980DF8CF</t>
         </is>
       </c>
@@ -3523,7 +3603,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3690,6 +3770,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>DEFADOL 160MG-5ML SUGAR FREE SYRUP</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-E19E2F704F51</t>
         </is>
       </c>
@@ -3713,7 +3798,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3876,6 +3961,11 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>DEFADOL 160MG-5ML SUGAR FREE SYRUP</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-96D4DBB9DC07</t>
         </is>
       </c>
@@ -3899,7 +3989,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4066,6 +4156,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>DEFADOL 160MG-5ML SUGAR FREE SYRUP</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-6BF96F3081B2</t>
         </is>
       </c>
@@ -4089,7 +4184,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4260,6 +4355,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>DECOZAL NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-F91272143AA7</t>
         </is>
       </c>
@@ -4283,7 +4383,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4454,6 +4554,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>DEFONASE SYRUP</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-4606EEFBC196</t>
         </is>
       </c>
@@ -4477,7 +4582,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4648,6 +4753,11 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>DECOZAL 0.1% NASAL DROPS</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-F78304255683</t>
         </is>
       </c>
@@ -4671,7 +4781,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4838,6 +4948,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>DECAPEPTYL 0.1MG S.C. Injection*</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-AB70F17D62F3</t>
         </is>
       </c>
@@ -4861,7 +4976,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5024,6 +5139,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>DECAL B12</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-F55E5C6C964B</t>
         </is>
       </c>
@@ -5047,7 +5167,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5218,6 +5338,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>DECOZAL 0.05% NASAL DROPS</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-0FFBE11B5FF6</t>
         </is>
       </c>
@@ -5241,7 +5366,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5404,6 +5529,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>CECLOR 125MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-811CA6D62320</t>
         </is>
       </c>
@@ -5427,7 +5557,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5600,6 +5730,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>DEFONEX 0.05% NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-00CAD0818FF9</t>
         </is>
       </c>
@@ -5623,7 +5758,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5782,6 +5917,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>DEFORAX 5% CREAM</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-DC89CDDFE89B</t>
         </is>
       </c>
@@ -5805,7 +5945,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5972,6 +6112,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>DEPRALEX 10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-5EEE2D1894EB</t>
         </is>
       </c>
@@ -5995,7 +6140,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6162,6 +6307,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>DEFOPAN 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-4B2BEBED2235</t>
         </is>
       </c>
@@ -6185,7 +6335,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6356,6 +6506,11 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>DEMENTILE 10MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-ABA357D3D871</t>
         </is>
       </c>
@@ -6379,7 +6534,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6538,6 +6693,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>DEFOSALIC OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-80E8E3F75694</t>
         </is>
       </c>
@@ -6561,7 +6721,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6724,6 +6884,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>DEFOSALIC OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-C356142FBF43</t>
         </is>
       </c>
@@ -6747,7 +6912,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6914,6 +7079,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>DEFOSALIC LOTION</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-A27D00F22D37</t>
         </is>
       </c>
@@ -6937,7 +7107,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7092,6 +7262,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>DEFORAX 5% CREAM</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-4BEEB304EF40</t>
         </is>
       </c>
@@ -7115,7 +7290,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7278,6 +7453,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>DEMENTILE 5MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-7AF42A64A245</t>
         </is>
       </c>
@@ -7301,7 +7481,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7464,6 +7644,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>CARVIDOL 6.25MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-3F0510E30D37</t>
         </is>
       </c>
@@ -7487,7 +7672,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7646,6 +7831,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>ANTACID JEDCO 480MG CHEWABLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-0DF3F48AD548</t>
         </is>
       </c>
@@ -7669,7 +7859,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7824,6 +8014,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>ANDROGEL 1% GEL</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-65034A45B6D7</t>
         </is>
       </c>
@@ -7847,7 +8042,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8018,6 +8213,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>ANDROCUR 50MG TAB</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-81353908C2D8</t>
         </is>
       </c>
@@ -8041,7 +8241,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8200,6 +8400,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>ANDREWS LIVER SALT SACHET 5GM</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-E737ED4C43D1</t>
         </is>
       </c>
@@ -8223,7 +8428,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8390,6 +8595,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>ANAZOL 500 MG F.C. TAB</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-4DD0F92A3A8D</t>
         </is>
       </c>
@@ -8413,7 +8623,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8584,6 +8794,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>ANAZOL 250 MG F.C. TAB</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-416CA8CF1BA0</t>
         </is>
       </c>
@@ -8607,7 +8822,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8774,6 +8989,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>ANAZOL 200MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-93001573F7D1</t>
         </is>
       </c>
@@ -8797,7 +9017,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8960,6 +9180,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>ANAZOL   125MG-5ML SUSP.</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-B36BD7E011B9</t>
         </is>
       </c>
@@ -8983,7 +9208,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9146,6 +9371,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>ANAFLEX POWDER</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-4AB1AF1AAD94</t>
         </is>
       </c>
@@ -9169,7 +9399,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9328,6 +9558,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>ANTIPLATE 75MG TAB</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-28DFEB0D5F11</t>
         </is>
       </c>
@@ -9351,7 +9586,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9522,6 +9757,11 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>APIMOL 0.5% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-26318BA121B6</t>
         </is>
       </c>
@@ -9545,7 +9785,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9712,6 +9952,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>APIMOL 0.25% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-E50FF6FB9691</t>
         </is>
       </c>
@@ -9735,7 +9980,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9898,6 +10143,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>APILLERG EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-ADD2983C0E78</t>
         </is>
       </c>
@@ -9921,7 +10171,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10084,6 +10334,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>APIHIST EYE\NOSE DROP</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-2237DA242F66</t>
         </is>
       </c>
@@ -10107,7 +10362,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10274,6 +10529,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>APIGEN 0.3% EYE OINTEMENT</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-BFA56CC6B1F9</t>
         </is>
       </c>
@@ -10297,7 +10557,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10468,6 +10728,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>APIGEN 0.3% E-E DROPS</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-60FB2FB5FDD2</t>
         </is>
       </c>
@@ -10491,7 +10756,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10662,6 +10927,11 @@
       </c>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>AMVASC 5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-46B9761CECF2</t>
         </is>
       </c>
@@ -10685,7 +10955,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10852,6 +11122,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>APIFLOX 0.3% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-B6A3BBA7356F</t>
         </is>
       </c>
@@ -10875,7 +11150,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11046,6 +11321,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>APICROM 2% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-79D9BC0CEBD0</t>
         </is>
       </c>
@@ -11069,7 +11349,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11236,6 +11516,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>APICORT FORTE 10MG-ML EYE SUSP.</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-0EF84C2ECD3F</t>
         </is>
       </c>
@@ -11259,7 +11544,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11426,6 +11711,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>APICORT 0.12% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-0A6F76E0330A</t>
         </is>
       </c>
@@ -11449,7 +11739,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11608,6 +11898,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>APICARPINE 4% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-7470BBAB08DD</t>
         </is>
       </c>
@@ -11631,7 +11926,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11802,6 +12097,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>APICARPINE 2% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-B423D5EA1D4F</t>
         </is>
       </c>
@@ -11825,7 +12125,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11998,6 +12298,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>APIDRA SOLOSTAR 100 U- ML DISPOSABLE PEN</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-C7075365F78A</t>
         </is>
       </c>
@@ -12021,7 +12326,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12192,6 +12497,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>AMVASC 2.5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-DE6FA76CEE05</t>
         </is>
       </c>
@@ -12215,7 +12525,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12386,6 +12696,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>AMRIZOLE SUSP 125MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-A98585B359CA</t>
         </is>
       </c>
@@ -12409,7 +12724,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12584,6 +12899,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>AMLOR CAPS 5MG</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-DB6448D44D33</t>
         </is>
       </c>
@@ -12607,7 +12927,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12778,6 +13098,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>AMLOR 10MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-9EC58712190D</t>
         </is>
       </c>
@@ -12801,7 +13126,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12972,6 +13297,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>AMLOPINE 5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-3AA6B33F7C8D</t>
         </is>
       </c>
@@ -12995,7 +13325,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13162,6 +13492,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>AMLOPINE 10MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-B95F49582BCF</t>
         </is>
       </c>
@@ -13185,7 +13520,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13356,6 +13691,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>AMLOCARD 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-9F4951A759DC</t>
         </is>
       </c>
@@ -13379,7 +13719,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13550,6 +13890,11 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>AMISTOP 5MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-793007B979CD</t>
         </is>
       </c>
@@ -13573,7 +13918,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13740,6 +14085,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>AMRIZOLE 500MG VAGINAL SUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-6EC6E6FF9836</t>
         </is>
       </c>
@@ -13763,7 +14113,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13934,6 +14284,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>AMRIZOLE 250 Mg TABLET</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-F7A6542FA0BF</t>
         </is>
       </c>
@@ -13957,7 +14312,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14124,6 +14479,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>AMVASC 10MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-B10C46FE40A5</t>
         </is>
       </c>
@@ -14147,7 +14507,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14310,6 +14670,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>AMOXIL POWDER FOR ORAL SUSPENSION 125MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-780D5AFE6B7A</t>
         </is>
       </c>
@@ -14333,7 +14698,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14504,6 +14869,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>AMOXIL 500MG CAP.</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-2752E7AEE008</t>
         </is>
       </c>
@@ -14527,7 +14897,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14698,6 +15068,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>AMOXIL 250MG CAP.</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-82A4636DE031</t>
         </is>
       </c>
@@ -14721,7 +15096,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14892,6 +15267,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>AMOXIL POWDER FOR ORAL SUSPENSION FORTE 250MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-679D769C9861</t>
         </is>
       </c>
@@ -14915,7 +15295,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15070,6 +15450,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>APO-DICLO 50 mg enteric-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-048C4F743430</t>
         </is>
       </c>
@@ -15093,7 +15478,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15266,6 +15651,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>ATACAND 8 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-081F9043F0BD</t>
         </is>
       </c>
@@ -15289,7 +15679,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15454,6 +15844,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>ATACAND 32MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-174DE21579C7</t>
         </is>
       </c>
@@ -15477,7 +15872,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15646,6 +16041,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>ATACAND 16 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-42FC8121C7EA</t>
         </is>
       </c>
@@ -15669,7 +16069,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15836,6 +16236,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>ASTATIN 40MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-3DA75B13E4B5</t>
         </is>
       </c>
@@ -15859,7 +16264,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16030,6 +16435,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>ASTATIN 20MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-35A2CE6855E5</t>
         </is>
       </c>
@@ -16053,7 +16463,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16224,6 +16634,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>ASTATIN 10MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-A8A340507AC8</t>
         </is>
       </c>
@@ -16247,7 +16662,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16406,6 +16821,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>ASPICOT 100 MG E.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-B7B6D1B5F909</t>
         </is>
       </c>
@@ -16429,7 +16849,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16588,6 +17008,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>ASPICOT 100 MG E.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-04F9BA9B7332</t>
         </is>
       </c>
@@ -16611,7 +17036,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16774,6 +17199,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>ASPICARD 81MG TAB</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-CA01BA3B7714</t>
         </is>
       </c>
@@ -16797,7 +17227,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16956,6 +17386,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>ASMADIL TABS 2MG</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-2908CD3C7B89</t>
         </is>
       </c>
@@ -16979,7 +17414,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17138,6 +17573,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>ASMADIL SYRUP</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-A068A18542D6</t>
         </is>
       </c>
@@ -17161,7 +17601,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17326,6 +17766,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>ATAPINA 100MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-24205031F9C8</t>
         </is>
       </c>
@@ -17349,7 +17794,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17520,6 +17965,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>ATORVA 10MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-DF9159B43C81</t>
         </is>
       </c>
@@ -17543,7 +17993,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17698,6 +18148,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>ATORVA 80MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-9EA6BA8A7EE7</t>
         </is>
       </c>
@@ -17721,7 +18176,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17892,6 +18347,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>ATORVA 40MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-E7FF58A00A1A</t>
         </is>
       </c>
@@ -17915,7 +18375,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18086,6 +18546,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>ATORVA 20MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-8B72CE89EDE9</t>
         </is>
       </c>
@@ -18109,7 +18574,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18276,6 +18741,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>ASACOL 800MG GASTRO-RESISTANT TABLETS</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-1DC2DB7FB648</t>
         </is>
       </c>
@@ -18299,7 +18769,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18456,6 +18926,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>ATAPINA 300MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-BF9ECD426A57</t>
         </is>
       </c>
@@ -18479,7 +18954,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18644,6 +19119,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>ATAPINA 25MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-79561E032165</t>
         </is>
       </c>
@@ -18667,7 +19147,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18832,6 +19312,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>ATAPINA 200MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-35B88B625687</t>
         </is>
       </c>
@@ -18855,7 +19340,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19018,6 +19503,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>ASACOL 500MG SUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-D614F2235480</t>
         </is>
       </c>
@@ -19041,7 +19531,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19212,6 +19702,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>ARTIZ 10 MG F.C TABLET</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-C9B51C6A195D</t>
         </is>
       </c>
@@ -19235,7 +19730,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19406,6 +19901,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>APPI- D 0.5MG-10ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-9CBA2279F638</t>
         </is>
       </c>
@@ -19429,7 +19929,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19591,6 +20091,11 @@
       <c r="AR101" t="inlineStr"/>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>APO-DOXY 100MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-3AF425A33F91</t>
         </is>
@@ -19607,7 +20112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19653,100 +20158,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19778,7 +20288,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19793,92 +20303,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-70181</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>115.81</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Home Health Test</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>73</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19910,7 +20425,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19925,92 +20440,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-76296</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>390.16</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>74</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20042,7 +20562,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20057,92 +20577,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-78515</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>473.97</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>75</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20174,7 +20699,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20189,92 +20714,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-74818</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>139.85</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>76</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20306,7 +20836,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20321,92 +20851,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-15323</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>99.13</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>77</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20438,7 +20973,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20453,92 +20988,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-53886</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>247.83</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>78</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20570,7 +21110,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20585,92 +21125,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-33424</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>398.22</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>79</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20702,7 +21247,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20717,92 +21262,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-45527</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>253.03</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>80</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20834,7 +21384,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20849,92 +21399,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-75410</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>131.31</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>81</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20966,7 +21521,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20981,92 +21536,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-79627</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>66.72</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>82</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21098,7 +21658,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21113,92 +21673,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-60164</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>319.09</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>83</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21230,7 +21795,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -21245,92 +21810,97 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>SKU-88399</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>74.69</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T13" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>84</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>100</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>12</v>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21347,7 +21917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21453,6 +22023,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21488,7 +22068,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21553,6 +22133,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-0279744F85CB</t>
         </is>
@@ -21589,7 +22179,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21654,6 +22244,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-29D51C0E9A4B</t>
         </is>
@@ -21690,7 +22290,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21755,6 +22355,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-084873E58E3C</t>
         </is>
@@ -21791,7 +22401,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21856,6 +22466,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-EF1A20921EA7</t>
         </is>
@@ -21892,7 +22512,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21957,6 +22577,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-12257236F3FD</t>
         </is>
@@ -21993,7 +22623,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -22058,6 +22688,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-2D7DE685A3B0</t>
         </is>
@@ -22094,7 +22734,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22159,6 +22799,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-CF760D2D11CB</t>
         </is>
@@ -22195,7 +22845,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22260,6 +22910,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-4A99F236B6B1</t>
         </is>
@@ -22296,7 +22956,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22361,6 +23021,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-EF1908C2486E</t>
         </is>
@@ -22397,7 +23067,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22462,6 +23132,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-E2A1F53C61B2</t>
         </is>
@@ -22498,7 +23178,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22563,6 +23243,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-0705A8B04596</t>
         </is>
@@ -22599,7 +23289,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22664,6 +23354,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-8143E1742FB5</t>
         </is>
@@ -22700,7 +23400,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22765,6 +23465,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-44A758944F13</t>
         </is>
@@ -22801,7 +23511,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22866,6 +23576,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-45D8D2A3CDD2</t>
         </is>
@@ -22902,7 +23622,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22967,6 +23687,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-6BF4287E7429</t>
         </is>
@@ -23003,7 +23733,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -23068,6 +23798,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-D91A5824B528</t>
         </is>
@@ -23104,7 +23844,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23169,6 +23909,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-5BFE7C43F6B0</t>
         </is>
@@ -23205,7 +23955,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23270,6 +24020,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-9FE8678C2350</t>
         </is>
@@ -23306,7 +24066,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23371,6 +24131,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-70C1B8DD54E3</t>
         </is>
@@ -23407,7 +24177,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23472,6 +24242,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-628A0088E1DC</t>
         </is>

--- a/product_upload/packages/16/file.xlsx
+++ b/product_upload/packages/16/file.xlsx
@@ -1084,8 +1084,16 @@
           <t>7259120116-311-860813660744</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXANOL CREAM 30 GM</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>DEXANOL CREAM 30 GM detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1665,8 +1673,16 @@
           <t>9504220857-924-734542017285</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DETRUSITOL RETARD 2 mg capsule</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>DETRUSITOL RETARD 2 mg capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -2453,8 +2469,16 @@
           <t>8997564988-975-499713849692</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEPRAN 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>DEPRAN 40 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2648,8 +2672,16 @@
           <t>4796698158-285-161599732842</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEPRAN 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>DEPRAN 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -3038,8 +3070,16 @@
           <t>7925412654-309-551389809121</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEFLAT 40 MG/ML ORAL DROPS</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>DEFLAT 40 MG/ML ORAL DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3806,8 +3846,16 @@
           <t>3066647030-482-382788433352</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEFADOL 160MG-5ML SUGAR FREE SYRUP</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>DEFADOL 160MG-5ML SUGAR FREE SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -4984,8 +5032,16 @@
           <t>7512453174-643-054858402190</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DECAL B12</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>DECAL B12 detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -5374,8 +5430,16 @@
           <t>2839204195-402-033587919824</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CECLOR 125MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CECLOR 125MG-5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5766,8 +5830,16 @@
           <t>0620026481-250-523601846672</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEFORAX 5% CREAM</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>DEFORAX 5% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -6542,8 +6614,16 @@
           <t>6182893006-517-325072478234</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEFOSALIC OINTMENT</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>DEFOSALIC OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6729,8 +6809,16 @@
           <t>7784854139-518-663568534179</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEFOSALIC OINTMENT</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>DEFOSALIC OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -7115,8 +7203,16 @@
           <t>8646202957-068-017710845607</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEFORAX 5% CREAM</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>DEFORAX 5% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7489,8 +7585,16 @@
           <t>4242511620-542-006500550334</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARVIDOL 6.25MG TABLET</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>CARVIDOL 6.25MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7680,8 +7784,16 @@
           <t>6511918492-961-534506394575</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ANTACID JEDCO 480MG CHEWABLE TABLETS</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ANTACID JEDCO 480MG CHEWABLE TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7867,8 +7979,16 @@
           <t>0522835688-380-084012230684</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ANDROGEL 1% GEL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ANDROGEL 1% GEL detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -8249,8 +8369,16 @@
           <t>2579564674-402-594293296058</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ANDREWS LIVER SALT SACHET 5GM</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ANDREWS LIVER SALT SACHET 5GM detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -9216,8 +9344,16 @@
           <t>5907508579-367-822139399023</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ANAFLEX POWDER</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ANAFLEX POWDER detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9407,8 +9543,16 @@
           <t>1918262067-088-169550268202</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ANTIPLATE 75MG TAB</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ANTIPLATE 75MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9988,8 +10132,16 @@
           <t>8112919282-358-743839717029</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ APILLERG EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>APILLERG EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10179,8 +10331,16 @@
           <t>4742239608-909-862776910233</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ APIHIST EYE\NOSE DROP</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>APIHIST EYE\NOSE DROP detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -11747,8 +11907,16 @@
           <t>7160406641-903-374068178178</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ APICARPINE 4% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>APICARPINE 4% EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -15303,8 +15471,16 @@
           <t>6750144336-768-878080702412</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ APO-DICLO 50 mg enteric-coated tablet</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>APO-DICLO 50 mg enteric-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15687,8 +15863,16 @@
           <t>5927887364-934-471441351294</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATACAND 32MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ATACAND 32MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
           <t>TABUK PHARMACEUTICAL MANUFACTURING CO.</t>
@@ -16670,8 +16854,16 @@
           <t>7630266600-383-446222926285</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ASPICOT 100 MG E.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ASPICOT 100 MG E.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16857,8 +17049,16 @@
           <t>1296971885-005-241830248085</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ASPICOT 100 MG E.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ASPICOT 100 MG E.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -17044,8 +17244,16 @@
           <t>9943409466-841-048451295630</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ASPICARD 81MG TAB</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ASPICARD 81MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -17235,8 +17443,16 @@
           <t>9503993648-267-755838387178</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ASMADIL TABS 2MG</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>ASMADIL TABS 2MG detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17422,8 +17638,16 @@
           <t>9785011594-010-631544529135</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ASMADIL SYRUP</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>ASMADIL SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17609,8 +17833,16 @@
           <t>1723651027-860-541366907078</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATAPINA 100MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ATAPINA 100MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>DEEF PHARMACEUTICAL INDUSTRIES</t>
@@ -18001,8 +18233,16 @@
           <t>2306042626-059-914715399105</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATORVA 80MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ATORVA 80MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18777,8 +19017,16 @@
           <t>1991768183-801-965644897236</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATAPINA 300MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ATAPINA 300MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
           <t>DEEF PHARMACEUTICAL INDUSTRIES</t>
@@ -18962,8 +19210,16 @@
           <t>3733380380-205-091200699624</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATAPINA 25MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>ATAPINA 25MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>DEEF PHARMACEUTICAL INDUSTRIES</t>
@@ -19155,8 +19411,16 @@
           <t>5856600223-703-626028704733</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATAPINA 200MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>ATAPINA 200MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>DEEF PHARMACEUTICAL INDUSTRIES</t>

--- a/product_upload/packages/16/file.xlsx
+++ b/product_upload/packages/16/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20422,7 +20422,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22181,7 +22181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22262,40 +22262,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22375,38 +22380,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>377.39</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-0279744F85CB</t>
         </is>
@@ -22486,38 +22496,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>120.52</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-29D51C0E9A4B</t>
         </is>
@@ -22597,38 +22612,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>69.31</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-084873E58E3C</t>
         </is>
@@ -22708,38 +22728,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>33.92</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-EF1A20921EA7</t>
         </is>
@@ -22819,38 +22844,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>347.84</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-12257236F3FD</t>
         </is>
@@ -22930,38 +22960,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>93.81</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-2D7DE685A3B0</t>
         </is>
@@ -23041,38 +23076,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>244.34</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-CF760D2D11CB</t>
         </is>
@@ -23152,38 +23192,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>396.23</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-4A99F236B6B1</t>
         </is>
@@ -23263,38 +23308,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>403.85</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-EF1908C2486E</t>
         </is>
@@ -23374,38 +23424,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>405.81</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-E2A1F53C61B2</t>
         </is>
@@ -23485,38 +23540,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>300.67</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-0705A8B04596</t>
         </is>
@@ -23596,38 +23656,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>260.51</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-8143E1742FB5</t>
         </is>
@@ -23707,38 +23772,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>321.93</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-44A758944F13</t>
         </is>
@@ -23818,38 +23888,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>485.68</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-45D8D2A3CDD2</t>
         </is>
@@ -23929,38 +24004,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>267.63</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-6BF4287E7429</t>
         </is>
@@ -24040,38 +24120,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>58.08</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-D91A5824B528</t>
         </is>
@@ -24151,38 +24236,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>184.7</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-5BFE7C43F6B0</t>
         </is>
@@ -24262,38 +24352,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>461.62</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-9FE8678C2350</t>
         </is>
@@ -24373,38 +24468,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>312.83</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-70C1B8DD54E3</t>
         </is>
@@ -24484,38 +24584,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>200.39</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-628A0088E1DC</t>
         </is>
